--- a/temp_doc/DATA KELAS FIX TRIAL.xlsx
+++ b/temp_doc/DATA KELAS FIX TRIAL.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10802"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Applications/XAMPP/xamppfiles/htdocs/cbt2.6admin/temp_doc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{770AC54F-541C-1E48-8D97-1D24FFFE9A52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FEE444E-0328-614A-AAE8-C67740FF48C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16100" xr2:uid="{AB72E732-1B4D-0449-8A67-D584FA100D85}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15840" xr2:uid="{AB72E732-1B4D-0449-8A67-D584FA100D85}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$D$29</definedName>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="39">
   <si>
     <t>id</t>
   </si>
@@ -124,61 +125,37 @@
     <t>XI DKV</t>
   </si>
   <si>
-    <t>X AKL 1_ULANGAN HARIAN_2025/2026</t>
-  </si>
-  <si>
-    <t>X AKL 2_ULANGAN HARIAN_2025/2026</t>
-  </si>
-  <si>
-    <t>X PM_ULANGAN HARIAN_2025/2026</t>
-  </si>
-  <si>
-    <t>X MPLB 1_ULANGAN HARIAN_2025/2026</t>
-  </si>
-  <si>
-    <t>X MPLB 2_ULANGAN HARIAN_2025/2026</t>
-  </si>
-  <si>
-    <t>X TJKT 1_ULANGAN HARIAN_2025/2026</t>
-  </si>
-  <si>
-    <t>X TJKT 2_ULANGAN HARIAN_2025/2026</t>
-  </si>
-  <si>
-    <t>X TJKT 3_ULANGAN HARIAN_2025/2026</t>
-  </si>
-  <si>
-    <t>X TJKT 4_ULANGAN HARIAN_2025/2026</t>
-  </si>
-  <si>
-    <t>X DKV_ULANGAN HARIAN_2025/2026</t>
-  </si>
-  <si>
-    <t>XI AKL 1_ULANGAN HARIAN_2025/2026</t>
-  </si>
-  <si>
-    <t>XI AKL 2_ULANGAN HARIAN_2025/2026</t>
-  </si>
-  <si>
-    <t>XI PM_ULANGAN HARIAN_2025/2026</t>
-  </si>
-  <si>
-    <t>XI MPLB 1_ULANGAN HARIAN_2025/2026</t>
-  </si>
-  <si>
-    <t>XI MPLB 2_ULANGAN HARIAN_2025/2026</t>
-  </si>
-  <si>
-    <t>XI TJKT 1_ULANGAN HARIAN_2025/2026</t>
-  </si>
-  <si>
-    <t>XI TJKT 2_ULANGAN HARIAN_2025/2026</t>
-  </si>
-  <si>
-    <t>XI TJKT 3_ULANGAN HARIAN_2025/2026</t>
-  </si>
-  <si>
-    <t>XI DKV_ULANGAN HARIAN_2025/2026</t>
+    <t>XI TJKT 4</t>
+  </si>
+  <si>
+    <t>XII AKL 1</t>
+  </si>
+  <si>
+    <t>XII AKL 2</t>
+  </si>
+  <si>
+    <t>XII PM</t>
+  </si>
+  <si>
+    <t>XII MPLB 1</t>
+  </si>
+  <si>
+    <t>XII MPLB 2</t>
+  </si>
+  <si>
+    <t>XII TJKT 1</t>
+  </si>
+  <si>
+    <t>XII TJKT 2</t>
+  </si>
+  <si>
+    <t>XII TJKT 3</t>
+  </si>
+  <si>
+    <t>XII TJKT 4</t>
+  </si>
+  <si>
+    <t>XII DKV</t>
   </si>
 </sst>
 </file>
@@ -545,7 +522,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{664577AF-41FC-0C49-BD7B-86162BAED619}">
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="4" max="4" width="31.33203125" bestFit="1" customWidth="1"/>
@@ -575,8 +552,9 @@
       <c r="C2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D2" t="s">
-        <v>28</v>
+      <c r="D2" t="str">
+        <f>_xlfn.CONCAT(C2,"_","TRIAL","_","2026/2027")</f>
+        <v>X AKL 1_TRIAL_2026/2027</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
@@ -589,8 +567,9 @@
       <c r="C3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D3" t="s">
-        <v>29</v>
+      <c r="D3" t="str">
+        <f t="shared" ref="D3:D30" si="0">_xlfn.CONCAT(C3,"_","TRIAL","_","2026/2027")</f>
+        <v>X AKL 2_TRIAL_2026/2027</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
@@ -603,8 +582,9 @@
       <c r="C4" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D4" t="s">
-        <v>30</v>
+      <c r="D4" t="str">
+        <f t="shared" si="0"/>
+        <v>X PM_TRIAL_2026/2027</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
@@ -617,8 +597,9 @@
       <c r="C5" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D5" t="s">
-        <v>31</v>
+      <c r="D5" t="str">
+        <f t="shared" si="0"/>
+        <v>X MPLB 1_TRIAL_2026/2027</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
@@ -631,8 +612,9 @@
       <c r="C6" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D6" t="s">
-        <v>32</v>
+      <c r="D6" t="str">
+        <f t="shared" si="0"/>
+        <v>X MPLB 2_TRIAL_2026/2027</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
@@ -645,8 +627,9 @@
       <c r="C7" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D7" t="s">
-        <v>33</v>
+      <c r="D7" t="str">
+        <f t="shared" si="0"/>
+        <v>X TJKT 1_TRIAL_2026/2027</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
@@ -659,8 +642,9 @@
       <c r="C8" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D8" t="s">
-        <v>34</v>
+      <c r="D8" t="str">
+        <f t="shared" si="0"/>
+        <v>X TJKT 2_TRIAL_2026/2027</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
@@ -673,8 +657,9 @@
       <c r="C9" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D9" t="s">
-        <v>35</v>
+      <c r="D9" t="str">
+        <f t="shared" si="0"/>
+        <v>X TJKT 3_TRIAL_2026/2027</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
@@ -687,8 +672,9 @@
       <c r="C10" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D10" t="s">
-        <v>36</v>
+      <c r="D10" t="str">
+        <f t="shared" si="0"/>
+        <v>X TJKT 4_TRIAL_2026/2027</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
@@ -701,8 +687,9 @@
       <c r="C11" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D11" t="s">
-        <v>37</v>
+      <c r="D11" t="str">
+        <f t="shared" si="0"/>
+        <v>X DKV_TRIAL_2026/2027</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
@@ -715,8 +702,9 @@
       <c r="C12" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D12" t="s">
-        <v>38</v>
+      <c r="D12" t="str">
+        <f t="shared" si="0"/>
+        <v>XI AKL 1_TRIAL_2026/2027</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
@@ -729,8 +717,9 @@
       <c r="C13" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D13" t="s">
-        <v>39</v>
+      <c r="D13" t="str">
+        <f t="shared" si="0"/>
+        <v>XI AKL 2_TRIAL_2026/2027</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
@@ -743,8 +732,9 @@
       <c r="C14" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D14" t="s">
-        <v>40</v>
+      <c r="D14" t="str">
+        <f t="shared" si="0"/>
+        <v>XI PM_TRIAL_2026/2027</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
@@ -757,8 +747,9 @@
       <c r="C15" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D15" t="s">
-        <v>41</v>
+      <c r="D15" t="str">
+        <f t="shared" si="0"/>
+        <v>XI MPLB 1_TRIAL_2026/2027</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
@@ -771,8 +762,9 @@
       <c r="C16" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D16" t="s">
-        <v>42</v>
+      <c r="D16" t="str">
+        <f t="shared" si="0"/>
+        <v>XI MPLB 2_TRIAL_2026/2027</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
@@ -785,8 +777,9 @@
       <c r="C17" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D17" t="s">
-        <v>43</v>
+      <c r="D17" t="str">
+        <f t="shared" si="0"/>
+        <v>XI TJKT 1_TRIAL_2026/2027</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
@@ -799,8 +792,9 @@
       <c r="C18" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="D18" t="s">
-        <v>44</v>
+      <c r="D18" t="str">
+        <f t="shared" si="0"/>
+        <v>XI TJKT 2_TRIAL_2026/2027</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
@@ -813,8 +807,9 @@
       <c r="C19" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D19" t="s">
-        <v>45</v>
+      <c r="D19" t="str">
+        <f t="shared" si="0"/>
+        <v>XI TJKT 3_TRIAL_2026/2027</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
@@ -822,44 +817,228 @@
         <v>1019</v>
       </c>
       <c r="B20" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D20" t="str">
+        <f t="shared" si="0"/>
+        <v>XI TJKT 4_TRIAL_2026/2027</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A21">
+        <v>1020</v>
+      </c>
+      <c r="B21" t="s">
         <v>4</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="C21" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D20" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="C21" s="2"/>
+      <c r="D21" t="str">
+        <f t="shared" si="0"/>
+        <v>XI DKV_TRIAL_2026/2027</v>
+      </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="C22" s="2"/>
+      <c r="A22">
+        <v>1021</v>
+      </c>
+      <c r="B22" t="s">
+        <v>3</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D22" t="str">
+        <f t="shared" si="0"/>
+        <v>XII AKL 1_TRIAL_2026/2027</v>
+      </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="C23" s="2"/>
+      <c r="A23">
+        <v>1022</v>
+      </c>
+      <c r="B23" t="s">
+        <v>3</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D23" t="str">
+        <f t="shared" si="0"/>
+        <v>XII AKL 2_TRIAL_2026/2027</v>
+      </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="C24" s="2"/>
+      <c r="A24">
+        <v>1023</v>
+      </c>
+      <c r="B24" t="s">
+        <v>5</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D24" t="str">
+        <f t="shared" si="0"/>
+        <v>XII PM_TRIAL_2026/2027</v>
+      </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="C25" s="2"/>
+      <c r="A25">
+        <v>1024</v>
+      </c>
+      <c r="B25" t="s">
+        <v>6</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D25" t="str">
+        <f t="shared" si="0"/>
+        <v>XII MPLB 1_TRIAL_2026/2027</v>
+      </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="C26" s="2"/>
+      <c r="A26">
+        <v>1025</v>
+      </c>
+      <c r="B26" t="s">
+        <v>6</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D26" t="str">
+        <f t="shared" si="0"/>
+        <v>XII MPLB 2_TRIAL_2026/2027</v>
+      </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="C27" s="2"/>
+      <c r="A27">
+        <v>1026</v>
+      </c>
+      <c r="B27" t="s">
+        <v>7</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D27" t="str">
+        <f t="shared" si="0"/>
+        <v>XII TJKT 1_TRIAL_2026/2027</v>
+      </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="C28" s="2"/>
+      <c r="A28">
+        <v>1027</v>
+      </c>
+      <c r="B28" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D28" t="str">
+        <f t="shared" si="0"/>
+        <v>XII TJKT 2_TRIAL_2026/2027</v>
+      </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="C29" s="2"/>
+      <c r="A29">
+        <v>1028</v>
+      </c>
+      <c r="B29" t="s">
+        <v>7</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D29" t="str">
+        <f t="shared" si="0"/>
+        <v>XII TJKT 3_TRIAL_2026/2027</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A30">
+        <v>1029</v>
+      </c>
+      <c r="B30" t="s">
+        <v>4</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D30" t="str">
+        <f t="shared" si="0"/>
+        <v>XII DKV_TRIAL_2026/2027</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26B4ADE2-3FAD-DE4B-ADBE-3FD4743899CD}">
+  <dimension ref="A1:A10"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A2" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A3" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A6" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A7" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A8" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A9" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A10" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>